--- a/Result/profitability/3540.xlsx
+++ b/Result/profitability/3540.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1874999999999999</v>
+        <v>0.3274999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>30.31875</v>
+        <v>30.90875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0.575</v>
+        <v>0.62</v>
       </c>
       <c r="N3" t="n">
-        <v>30.77875</v>
+        <v>30.795</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9099999999999999</v>
+        <v>0.8362499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>30.76625</v>
+        <v>30.66875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8737499999999999</v>
+        <v>0.9474999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>30.49625</v>
+        <v>29.885</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.99625</v>
+        <v>0.94125</v>
       </c>
       <c r="N6" t="n">
-        <v>30.015</v>
+        <v>29.94</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9475</v>
+        <v>0.915</v>
       </c>
       <c r="N7" t="n">
-        <v>30.23875</v>
+        <v>30.64875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.93875</v>
+        <v>0.9212499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>30.33</v>
+        <v>30.65875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D75" t="n">
+        <v>704</v>
+      </c>
+      <c r="E75" t="n">
+        <v>312</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07000000000000006</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.17875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09356101031661335</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.017241379310345</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.890000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.137243895593601</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
